--- a/output/pdf_financials_xlsx/SALT.xlsx
+++ b/output/pdf_financials_xlsx/SALT.xlsx
@@ -6278,7 +6278,7 @@
         <v>-0.030379</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>-0.057964</v>
+        <v>-0.056524</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>-0.892412</v>
@@ -24816,7 +24816,11 @@
           <t>Exploration and evaluation expense</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SALT.xlsx
+++ b/output/pdf_financials_xlsx/SALT.xlsx
@@ -978,19 +978,19 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002914</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004173</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002493</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000358</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000348</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1832,19 +1832,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.113451</v>
+        <v>-0.116365</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.261927</v>
+        <v>-0.2661</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.191213</v>
+        <v>-0.193706</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.170113</v>
+        <v>-0.170471</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.141131</v>
+        <v>-0.141479</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.196193</v>
@@ -1940,19 +1940,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.113451</v>
+        <v>-0.116365</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.261927</v>
+        <v>-0.2661</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.191213</v>
+        <v>-0.193706</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.170113</v>
+        <v>-0.170471</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.141131</v>
+        <v>-0.141479</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.195668</v>
@@ -2199,25 +2199,25 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.6506960000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.211547</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.149635</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.245276</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.065833</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001755</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.266831</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>8.804145999999999</v>
@@ -2226,7 +2226,7 @@
         <v>9.269788</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>9.269788</v>
+        <v>12.192483</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>8.032909999999999</v>
@@ -2295,25 +2295,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.6506960000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.211547</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.149635</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.245276</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.065833</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001755</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.266831</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>8.804145999999999</v>
@@ -2322,7 +2322,7 @@
         <v>9.269788</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>9.269788</v>
+        <v>12.192483</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>8.032909999999999</v>
@@ -2871,25 +2871,25 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.66254</v>
+        <v>0.011844</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.304807</v>
+        <v>0.09326</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.241853</v>
+        <v>0.09221799999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.256151</v>
+        <v>0.010875</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.07432</v>
+        <v>0.008487</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.00706</v>
+        <v>0.005305</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.271486</v>
+        <v>0.004655</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.018313</v>
@@ -2898,7 +2898,7 @@
         <v>0.028187</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.967526</v>
+        <v>0.044831</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.134871</v>
@@ -6578,10 +6578,10 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.015024</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019122</v>
       </c>
     </row>
     <row r="125">
@@ -6626,10 +6626,10 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.015024</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019122</v>
       </c>
     </row>
     <row r="126">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -17489,7 +17489,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -20526,7 +20526,11 @@
           <t>Right of use lease payments</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -22175,7 +22179,11 @@
           <t>Right of use Lease payments (Note 5)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -29584,7 +29592,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -30536,7 +30544,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -30864,7 +30872,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">

--- a/output/pdf_financials_xlsx/SALT.xlsx
+++ b/output/pdf_financials_xlsx/SALT.xlsx
@@ -577,15 +577,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -626,20 +622,14 @@
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -685,15 +675,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -711,16 +697,16 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
@@ -729,25 +715,19 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.083413</v>
+        <v>0.108413</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.211102</v>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.261102</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
@@ -788,20 +768,14 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -842,20 +816,14 @@
       <c r="K9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -879,10 +847,10 @@
         <v>0.193706</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
@@ -891,25 +859,19 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.083413</v>
+        <v>0.108413</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.211102</v>
-      </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.261102</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="11">
@@ -933,10 +895,10 @@
         <v>-0.193706</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-0.0125</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-0.0125</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
@@ -945,25 +907,21 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.083413</v>
+        <v>-0.108413</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.211102</v>
+        <v>-0.261102</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M11" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="12">
@@ -1004,20 +962,14 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1058,20 +1010,14 @@
       <c r="K13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -1112,20 +1058,14 @@
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1166,20 +1106,14 @@
       <c r="K15" s="3" t="n">
         <v>0.07940999999999999</v>
       </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1220,20 +1154,14 @@
       <c r="K16" s="3" t="n">
         <v>-2.45306</v>
       </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L16" s="3" t="n">
+        <v>-4.838013</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>-0.709145</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>-0.215137</v>
       </c>
     </row>
     <row r="17">
@@ -1274,20 +1202,14 @@
       <c r="K17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1472,20 +1394,14 @@
       <c r="K20" s="3" t="n">
         <v>-2.45306</v>
       </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L20" s="3" t="n">
+        <v>-4.838013</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>-0.709145</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>-0.215137</v>
       </c>
     </row>
     <row r="21">
@@ -1526,20 +1442,14 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1580,20 +1490,14 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1638,10 +1542,10 @@
         <v>-4.838013</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-3.675923</v>
+        <v>-0.709145</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>-3.712415</v>
+        <v>-0.215137</v>
       </c>
     </row>
     <row r="24">
@@ -1858,20 +1762,14 @@
       <c r="K27" s="3" t="n">
         <v>-2.45306</v>
       </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L27" s="3" t="n">
+        <v>-4.838013</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>-0.709145</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>-0.215137</v>
       </c>
     </row>
     <row r="28">
@@ -1912,20 +1810,14 @@
       <c r="K28" s="3" t="n">
         <v>0.003393</v>
       </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L28" s="3" t="n">
+        <v>0.012908</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0.026915</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0.035952</v>
       </c>
     </row>
     <row r="29">
@@ -1966,20 +1858,14 @@
       <c r="K29" s="3" t="n">
         <v>-2.449667</v>
       </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L29" s="3" t="n">
+        <v>-4.825105</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>-0.68223</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>-0.179185</v>
       </c>
     </row>
     <row r="30">
@@ -2092,20 +1978,14 @@
       <c r="K31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -7163,7 +7043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q302"/>
+  <dimension ref="A1:Q363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27453,12 +27333,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>5.    CAPITAL ASSETS</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Gain on investment in associate (Note 5)</t>
+          <t>Buildings 325,273 - 325,273 16,040 11,360</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -27507,23 +27387,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N256" s="5" t="n">
-        <v>0.739049</v>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P256" s="5" t="n">
+        <v>0.297873</v>
+      </c>
+      <c r="Q256" s="5" t="n">
+        <v>0.0274</v>
       </c>
     </row>
     <row r="257">
@@ -27534,12 +27412,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>5.    CAPITAL ASSETS</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Dilution gain (Note 5)</t>
+          <t>Land 373,118 74,041 447,159 - -</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -27588,18 +27466,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N257" s="5" t="n">
-        <v>0.40962</v>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P257" s="5" t="n">
+        <v>0.447159</v>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
@@ -27615,12 +27493,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>5.    CAPITAL ASSETS</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation assets (Note 6)</t>
+          <t>Office Furniture 12,617 - 12,617 3,344 1,855</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -27669,23 +27547,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N258" s="5" t="n">
-        <v>0.248911</v>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P258" s="5" t="n">
+        <v>0.007418</v>
+      </c>
+      <c r="Q258" s="5" t="n">
+        <v>0.005199</v>
       </c>
     </row>
     <row r="259">
@@ -27696,12 +27572,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>Computer</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Computer equipment 76,574 - 76,574 27,561 14,704</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -27745,26 +27621,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M259" s="5" t="n">
-        <v>0.020517</v>
-      </c>
-      <c r="N259" s="5" t="n">
-        <v>0.151873</v>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P259" s="5" t="n">
+        <v>0.034309</v>
+      </c>
+      <c r="Q259" s="5" t="n">
+        <v>0.042265</v>
       </c>
     </row>
     <row r="260">
@@ -27775,19 +27651,15 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>Light Duty</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Vehicle - 107,102 107,102 - 8,033</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -27828,26 +27700,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M260" s="5" t="n">
-        <v>0.053924</v>
-      </c>
-      <c r="N260" s="5" t="n">
-        <v>0.07940999999999999</v>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P260" s="5" t="n">
+        <v>0.099069</v>
+      </c>
+      <c r="Q260" s="5" t="n">
+        <v>0.008033</v>
       </c>
     </row>
     <row r="261">
@@ -27858,12 +27730,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>787,582   181,143    968,725        46,945      35,952      82,897   885,828 Total</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10)</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -27907,26 +27779,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M261" s="5" t="n">
-        <v>-0.986461</v>
-      </c>
-      <c r="N261" s="5" t="n">
-        <v>-1.80447</v>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P261" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="Q261" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="262">
@@ -27937,12 +27809,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>787,582   181,143    968,725        46,945      35,952      82,897   885,828 Total</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Marketing and communications</t>
+          <t>Buildings 286,740 38,533 325,273 5,735 10,304</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -27986,26 +27858,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M262" s="5" t="n">
-        <v>-0.651855</v>
-      </c>
-      <c r="N262" s="5" t="n">
-        <v>-0.793412</v>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P262" s="5" t="n">
+        <v>0.309235</v>
+      </c>
+      <c r="Q262" s="5" t="n">
+        <v>0.016039</v>
       </c>
     </row>
     <row r="263">
@@ -28016,19 +27888,15 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>787,582   181,143    968,725        46,945      35,952      82,897   885,828 Total</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Transfer agent, regulatory and professional fees</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Land 71,685 301,433 373,118 - -</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -28069,21 +27937,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M263" s="5" t="n">
-        <v>-0.093818</v>
-      </c>
-      <c r="N263" s="5" t="n">
-        <v>-0.433881</v>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P263" s="5" t="n">
+        <v>0.373118</v>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
@@ -28099,12 +27969,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>787,582   181,143    968,725        46,945      35,952      82,897   885,828 Total</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Management and subcontract fees (Note 11)</t>
+          <t>Office Furniture 12,617 - 12,617 1,262 2,082</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -28148,26 +28018,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M264" s="5" t="n">
-        <v>-0.196916</v>
-      </c>
-      <c r="N264" s="5" t="n">
-        <v>-0.370687</v>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P264" s="5" t="n">
+        <v>0.009273999999999999</v>
+      </c>
+      <c r="Q264" s="5" t="n">
+        <v>0.003344</v>
       </c>
     </row>
     <row r="265">
@@ -28178,12 +28048,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>Computer</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Office and other (Note11)</t>
+          <t>Computer equipment 35,075 41,499 76,574 13,031 14,530</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -28227,26 +28097,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M265" s="5" t="n">
-        <v>-0.207544</v>
-      </c>
-      <c r="N265" s="5" t="n">
-        <v>-0.234003</v>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P265" s="5" t="n">
+        <v>0.049013</v>
+      </c>
+      <c r="Q265" s="5" t="n">
+        <v>0.027561</v>
       </c>
     </row>
     <row r="266">
@@ -28257,19 +28127,15 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>Computer</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Totals 406,117 381,465 787,582 20,028 26,915</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -28310,26 +28176,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M266" s="5" t="n">
-        <v>0.083413</v>
-      </c>
-      <c r="N266" s="5" t="n">
-        <v>0.211102</v>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P266" s="5" t="n">
+        <v>0.74064</v>
+      </c>
+      <c r="Q266" s="5" t="n">
+        <v>0.046945</v>
       </c>
     </row>
     <row r="267">
@@ -28340,12 +28206,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>6.   INVESTMENTS</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Conferences and travel</t>
+          <t>December 31, 2025 December</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -28389,26 +28255,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M267" s="5" t="n">
-        <v>-2.2e-05</v>
-      </c>
-      <c r="N267" s="5" t="n">
-        <v>-0.118809</v>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P267" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="Q267" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="268">
@@ -28419,12 +28285,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>6.   INVESTMENTS</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Loss from equity accounted investment (Note 5)</t>
+          <t>Balance beginning of the year</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -28473,23 +28339,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N268" s="5" t="n">
-        <v>-0.062166</v>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P268" s="5" t="n">
+        <v>1.413113</v>
+      </c>
+      <c r="Q268" s="5" t="n">
+        <v>0.811142</v>
       </c>
     </row>
     <row r="269">
@@ -28500,15 +28364,19 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>6.   INVESTMENTS</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Directors' fees</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>Share of net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -28549,26 +28417,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M269" s="5" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="N269" s="5" t="n">
-        <v>-0.05</v>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O269" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P269" s="5" t="n">
+        <v>-0.709145</v>
+      </c>
+      <c r="Q269" s="5" t="n">
+        <v>-0.215137</v>
       </c>
     </row>
     <row r="270">
@@ -28579,19 +28447,15 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>6.   INVESTMENTS</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Dilution gain</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -28632,21 +28496,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M270" s="5" t="n">
-        <v>-0.001402</v>
-      </c>
-      <c r="N270" s="5" t="n">
-        <v>-0.003393</v>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P270" s="5" t="n">
+        <v>0.107173</v>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
@@ -28662,19 +28528,15 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>6.   INVESTMENTS</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on derecognition of associate</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -28715,11 +28577,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M271" s="5" t="n">
-        <v>-2.17199</v>
-      </c>
-      <c r="N271" s="5" t="n">
-        <v>-2.45306</v>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -28731,10 +28597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q271" s="5" t="n">
+        <v>0.776644</v>
       </c>
     </row>
     <row r="272">
@@ -28745,19 +28609,15 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Gain on disposal of mineral exploration and evaluation</t>
+          <t>6.   INVESTMENTS</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Net loss per share - basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Balance end of the year</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -28798,26 +28658,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M272" s="5" t="n">
-        <v>-3.1e-08</v>
-      </c>
-      <c r="N272" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O272" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P272" s="5" t="n">
+        <v>0.811142</v>
+      </c>
+      <c r="Q272" s="5" t="n">
+        <v>1.372649</v>
       </c>
     </row>
     <row r="273">
@@ -28828,59 +28688,75 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Weighted-average number of common shares outstanding -</t>
+          <t>near St. George’s, Western Newfoundland.</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Weighted-average number of common shares outstanding - basic and diluted</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
-      <c r="E273" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="F273" s="5" t="n">
-        <v>13.227399</v>
-      </c>
-      <c r="G273" s="5" t="n">
-        <v>36.883566</v>
-      </c>
-      <c r="H273" s="5" t="n">
-        <v>40.916671</v>
-      </c>
-      <c r="I273" s="5" t="n">
-        <v>43.420837</v>
-      </c>
-      <c r="J273" s="5" t="n">
-        <v>48.050004</v>
-      </c>
-      <c r="K273" s="5" t="n">
-        <v>48.050004</v>
-      </c>
-      <c r="L273" s="5" t="n">
-        <v>50.600004</v>
-      </c>
-      <c r="M273" s="5" t="n">
-        <v>69.573459</v>
-      </c>
-      <c r="N273" s="5" t="n">
-        <v>82.82726</v>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P273" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="Q273" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="274">
@@ -28891,12 +28767,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>Mineral Exploration and</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Management and subcontract fees (Note 10)</t>
+          <t>Evaluation Assets 11,782,322 5,022,655 (111,187)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -28930,11 +28806,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K274" s="5" t="n">
-        <v>-0.0105</v>
-      </c>
-      <c r="L274" s="5" t="n">
-        <v>-0.022487</v>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
@@ -28956,10 +28836,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q274" s="5" t="n">
+        <v>16.69379</v>
       </c>
     </row>
     <row r="275">
@@ -28970,19 +28848,15 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>Mineral Exploration and</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Transfer agent, regulatory and professional fees</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -28998,20 +28872,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H275" s="5" t="n">
-        <v>-0.043224</v>
-      </c>
-      <c r="I275" s="5" t="n">
-        <v>-0.05615</v>
-      </c>
-      <c r="J275" s="5" t="n">
-        <v>-0.039993</v>
-      </c>
-      <c r="K275" s="5" t="n">
-        <v>-0.041505</v>
-      </c>
-      <c r="L275" s="5" t="n">
-        <v>-0.041446</v>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
@@ -29028,15 +28912,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P275" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="Q275" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="276">
@@ -29047,12 +28927,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>Mineral Exploration and</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Office and other</t>
+          <t>Evaluation Assets 8,162,295 3,620,027 -</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -29071,20 +28951,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H276" s="5" t="n">
-        <v>-0.03631</v>
-      </c>
-      <c r="I276" s="5" t="n">
-        <v>-0.033782</v>
-      </c>
-      <c r="J276" s="5" t="n">
-        <v>-0.027721</v>
-      </c>
-      <c r="K276" s="5" t="n">
-        <v>-0.023832</v>
-      </c>
-      <c r="L276" s="5" t="n">
-        <v>-0.043516</v>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
@@ -29101,10 +28991,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P276" s="5" t="n">
+        <v>11.782322</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -29120,12 +29008,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>8.   RELATED PARTY TRANSACTIONS</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Conferences and travel</t>
+          <t>Vulcan Minerals Inc. owned 27.02% of the Company’s common shares at December</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -29144,20 +29032,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H277" s="5" t="n">
-        <v>-0.000223</v>
-      </c>
-      <c r="I277" s="5" t="n">
-        <v>-0.003115</v>
-      </c>
-      <c r="J277" s="5" t="n">
-        <v>-0.001138</v>
-      </c>
-      <c r="K277" s="5" t="n">
-        <v>-0.008562999999999999</v>
-      </c>
-      <c r="L277" s="5" t="n">
-        <v>-0.026313</v>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
@@ -29174,15 +29072,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P277" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="Q277" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="278">
@@ -29193,19 +29087,15 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>transactions were carried out with Vulcan Minerals Inc.</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Mineral exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -29236,11 +29126,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K278" s="5" t="n">
-        <v>-0.000525</v>
-      </c>
-      <c r="L278" s="5" t="n">
-        <v>-0.000525</v>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
@@ -29257,15 +29151,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P278" s="5" t="n">
+        <v>0.026857</v>
+      </c>
+      <c r="Q278" s="5" t="n">
+        <v>0.008911000000000001</v>
       </c>
     </row>
     <row r="279">
@@ -29276,12 +29166,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>transactions were carried out with Vulcan Minerals Inc.</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expense</t>
+          <t>Royalty</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -29310,16 +29200,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J279" s="5" t="n">
-        <v>-0.003918</v>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L279" s="5" t="n">
-        <v>-0.00144</v>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
@@ -29341,10 +29235,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q279" s="5" t="n">
+        <v>0.003684</v>
       </c>
     </row>
     <row r="280">
@@ -29355,15 +29247,19 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>transactions were carried out with Vulcan Minerals Inc.</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 9 (b))</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -29379,20 +29275,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H280" s="5" t="n">
-        <v>-0.013105</v>
-      </c>
-      <c r="I280" s="5" t="n">
-        <v>-0.002144</v>
-      </c>
-      <c r="J280" s="5" t="n">
-        <v>-0.02466</v>
-      </c>
-      <c r="K280" s="5" t="n">
-        <v>-0.111268</v>
-      </c>
-      <c r="L280" s="5" t="n">
-        <v>-0.078171</v>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
@@ -29409,15 +29315,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P280" s="5" t="n">
+        <v>0.031914</v>
+      </c>
+      <c r="Q280" s="5" t="n">
+        <v>0.000815</v>
       </c>
     </row>
     <row r="281">
@@ -29428,19 +29330,15 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>transactions were carried out with Vulcan Minerals Inc.</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Rent paid to a corporation which is controlled by a</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -29456,20 +29354,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H281" s="5" t="n">
-        <v>-0.191213</v>
-      </c>
-      <c r="I281" s="5" t="n">
-        <v>-0.170113</v>
-      </c>
-      <c r="J281" s="5" t="n">
-        <v>-0.141131</v>
-      </c>
-      <c r="K281" s="5" t="n">
-        <v>-0.196193</v>
-      </c>
-      <c r="L281" s="5" t="n">
-        <v>-0.213898</v>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
@@ -29486,10 +29394,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P281" s="5" t="n">
+        <v>0.012</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -29505,19 +29411,15 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>director of the Company</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Net loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>director of the Company total</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -29533,20 +29435,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H282" s="5" t="n">
-        <v>-5e-09</v>
-      </c>
-      <c r="I282" s="5" t="n">
-        <v>-4e-09</v>
-      </c>
-      <c r="J282" s="5" t="n">
-        <v>-3e-09</v>
-      </c>
-      <c r="K282" s="5" t="n">
-        <v>-4e-09</v>
-      </c>
-      <c r="L282" s="5" t="n">
-        <v>-4e-09</v>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
@@ -29563,15 +29475,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P282" s="5" t="n">
+        <v>0.070771</v>
+      </c>
+      <c r="Q282" s="5" t="n">
+        <v>0.01341</v>
       </c>
     </row>
     <row r="283">
@@ -29582,17 +29490,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>director of the Company</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Directors’ fees</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -29610,14 +29518,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H283" s="5" t="n">
-        <v>0.002493</v>
-      </c>
-      <c r="I283" s="5" t="n">
-        <v>0.000358</v>
-      </c>
-      <c r="J283" s="5" t="n">
-        <v>0.000348</v>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -29644,15 +29558,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P283" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Q283" s="5" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="284">
@@ -29663,19 +29573,15 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>director of the Company</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Other income (Note 8 (c ))</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Management and subcontractor fees</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -29701,8 +29607,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J284" s="5" t="n">
-        <v>0.0025</v>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -29729,15 +29637,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P284" s="5" t="n">
+        <v>0.747525</v>
+      </c>
+      <c r="Q284" s="5" t="n">
+        <v>1.230244</v>
       </c>
     </row>
     <row r="285">
@@ -29748,15 +29652,19 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Management and subcontract fees</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -29772,14 +29680,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H285" s="5" t="n">
-        <v>-0.08834400000000001</v>
-      </c>
-      <c r="I285" s="5" t="n">
-        <v>-0.06278</v>
-      </c>
-      <c r="J285" s="5" t="n">
-        <v>-0.034049</v>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -29806,15 +29720,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P285" s="5" t="n">
+        <v>1.300187</v>
+      </c>
+      <c r="Q285" s="5" t="n">
+        <v>0.159621</v>
       </c>
     </row>
     <row r="286">
@@ -29825,12 +29735,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Income (Expenses)</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Directors' fees</t>
+          <t>Mineral exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -29849,14 +29759,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H286" s="5" t="n">
-        <v>-0.0125</v>
-      </c>
-      <c r="I286" s="5" t="n">
-        <v>-0.0125</v>
-      </c>
-      <c r="J286" s="5" t="n">
-        <v>-0.0125</v>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -29883,15 +29799,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P286" s="5" t="n">
+        <v>0.564294</v>
+      </c>
+      <c r="Q286" s="5" t="n">
+        <v>-0.272615</v>
       </c>
     </row>
     <row r="287">
@@ -29902,12 +29814,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Management and subcontract fees</t>
+          <t>Share-based compensation total</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -29916,14 +29828,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F287" s="5" t="n">
-        <v>0.071543</v>
-      </c>
-      <c r="G287" s="5" t="n">
-        <v>0.120437</v>
-      </c>
-      <c r="H287" s="5" t="n">
-        <v>0.08834400000000001</v>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -29960,15 +29878,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P287" s="5" t="n">
+        <v>2.857399</v>
+      </c>
+      <c r="Q287" s="5" t="n">
+        <v>1.278294</v>
       </c>
     </row>
     <row r="288">
@@ -29979,32 +29893,34 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>9.   LONG TERM DEBT</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Transfer agent, regulatory and professional fees</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>at 5.52%. Combined principal and interest payments total $1,429 monthly. The loan matures on June</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F288" s="5" t="n">
-        <v>0.027569</v>
-      </c>
-      <c r="G288" s="5" t="n">
-        <v>0.045395</v>
-      </c>
-      <c r="H288" s="5" t="n">
-        <v>0.043224</v>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -30041,15 +29957,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P288" s="5" t="n">
+        <v>0.002032</v>
+      </c>
+      <c r="Q288" s="5" t="n">
+        <v>1.6e-05</v>
       </c>
     </row>
     <row r="289">
@@ -30060,12 +29972,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>9.   LONG TERM DEBT</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Office and other</t>
+          <t>Balance beginning of the year</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -30074,14 +29986,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F289" s="5" t="n">
-        <v>0.005466</v>
-      </c>
-      <c r="G289" s="5" t="n">
-        <v>0.036278</v>
-      </c>
-      <c r="H289" s="5" t="n">
-        <v>0.03631</v>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -30123,10 +30041,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q289" s="5" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="290">
@@ -30137,12 +30053,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>9.   LONG TERM DEBT</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 9 b))</t>
+          <t>Additions</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -30156,11 +30072,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G290" s="5" t="n">
-        <v>0.02711</v>
-      </c>
-      <c r="H290" s="5" t="n">
-        <v>0.013105</v>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -30197,15 +30117,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P290" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q290" s="5" t="n">
+        <v>0.107102</v>
       </c>
     </row>
     <row r="291">
@@ -30216,12 +30132,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>9.   LONG TERM DEBT</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Conferences and travel</t>
+          <t>Payments made</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -30230,14 +30146,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F291" s="5" t="n">
-        <v>0.011787</v>
-      </c>
-      <c r="G291" s="5" t="n">
-        <v>0.017952</v>
-      </c>
-      <c r="H291" s="5" t="n">
-        <v>0.000223</v>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -30279,10 +30201,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q291" s="5" t="n">
+        <v>-0.023958</v>
       </c>
     </row>
     <row r="292">
@@ -30293,12 +30213,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>9.   LONG TERM DEBT</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Directors' fees</t>
+          <t>Balance end of the year</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -30312,11 +30232,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G292" s="5" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="H292" s="5" t="n">
-        <v>0.0125</v>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
@@ -30353,15 +30277,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P292" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q292" s="5" t="n">
+        <v>0.183144</v>
       </c>
     </row>
     <row r="293">
@@ -30372,12 +30292,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>9.   LONG TERM DEBT</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Website development</t>
+          <t>Long term portion</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -30391,8 +30311,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G293" s="5" t="n">
-        <v>0.006428</v>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -30434,15 +30356,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P293" s="5" t="n">
+        <v>0.08964</v>
+      </c>
+      <c r="Q293" s="5" t="n">
+        <v>0.150925</v>
       </c>
     </row>
     <row r="294">
@@ -30453,32 +30371,34 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>9.   LONG TERM DEBT</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>General and administrative expenses total</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Short term portion</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F294" s="5" t="n">
-        <v>0.116365</v>
-      </c>
-      <c r="G294" s="5" t="n">
-        <v>0.2661</v>
-      </c>
-      <c r="H294" s="5" t="n">
-        <v>0.193706</v>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
@@ -30515,15 +30435,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P294" s="5" t="n">
+        <v>0.01036</v>
+      </c>
+      <c r="Q294" s="5" t="n">
+        <v>0.032219</v>
       </c>
     </row>
     <row r="295">
@@ -30534,32 +30450,34 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Future minimum long-term debt payments are as follows</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Fiscal year</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F295" s="5" t="n">
-        <v>0.002914</v>
-      </c>
-      <c r="G295" s="5" t="n">
-        <v>0.004173</v>
-      </c>
-      <c r="H295" s="5" t="n">
-        <v>0.002493</v>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -30596,15 +30514,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P295" s="5" t="n">
+        <v>0.032219</v>
+      </c>
+      <c r="Q295" s="5" t="n">
+        <v>0.002026</v>
       </c>
     </row>
     <row r="296">
@@ -30615,32 +30529,34 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Cost                Depreciation                  Value</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Buildings - 286,740 - 5,735</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F296" s="5" t="n">
-        <v>-0.113451</v>
-      </c>
-      <c r="G296" s="5" t="n">
-        <v>-0.261927</v>
-      </c>
-      <c r="H296" s="5" t="n">
-        <v>-0.191213</v>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -30672,10 +30588,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O296" s="5" t="n">
+        <v>0.281005</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -30696,32 +30610,34 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Cost                Depreciation                  Value</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Net loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Land - 71,685 - -</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F297" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="G297" s="5" t="n">
-        <v>-7e-09</v>
-      </c>
-      <c r="H297" s="5" t="n">
-        <v>-5e-09</v>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -30753,10 +30669,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O297" s="5" t="n">
+        <v>0.071685</v>
       </c>
       <c r="P297" t="inlineStr">
         <is>
@@ -30777,26 +30691,24 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Expenses (Other Income)</t>
+          <t>Cost                Depreciation                  Value</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>General and administrative (Note 10 &amp; 11) $</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Office - 12,617 - 1,262</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F298" s="5" t="n">
-        <v>0.116365</v>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -30838,10 +30750,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O298" s="5" t="n">
+        <v>0.011355</v>
       </c>
       <c r="P298" t="inlineStr">
         <is>
@@ -30862,26 +30772,24 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Expenses (Other Income)</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Computer 7,072 - 1,061 1,803</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F299" s="5" t="n">
-        <v>-0.002914</v>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -30923,10 +30831,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O299" s="5" t="n">
+        <v>0.004208</v>
       </c>
       <c r="P299" t="inlineStr">
         <is>
@@ -30947,26 +30853,24 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Expenses (Other Income)</t>
+          <t>– Server</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Net loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Computer 11,500 16,503 6,059 4,108</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F300" s="5" t="n">
-        <v>-0.113451</v>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -31008,10 +30912,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O300" s="5" t="n">
+        <v>0.017836</v>
       </c>
       <c r="P300" t="inlineStr">
         <is>
@@ -31032,26 +30934,24 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Expenses (Other Income)</t>
+          <t>Computer</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Total 18,572 387,545 7,120 12,908</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F301" s="5" t="n">
-        <v>-0.113451</v>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -31093,10 +30993,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O301" s="5" t="n">
+        <v>0.386089</v>
       </c>
       <c r="P301" t="inlineStr">
         <is>
@@ -31117,78 +31015,4971 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
+          <t>Computer</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>December 31,</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O302" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Cost                Depreciation                  Value</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Computer - 7,072 - 1,061</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O303" s="5" t="n">
+        <v>0.006011</v>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>– Server</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Computer 11,500 - 3,727 2,332</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O304" s="5" t="n">
+        <v>0.005441</v>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Computer</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Total 11,500 7,072 3,727 3,393</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O305" s="5" t="n">
+        <v>0.011452</v>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>6.  INVESTMENT IN ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>December 31 December</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O306" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>6.  INVESTMENT IN ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>6.  INVESTMENT IN ASSOCIATE total</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>6.  INVESTMENT IN ASSOCIATE</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Investment in Triple Point Resources Ltd. 1,413,113</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O308" s="5" t="n">
+        <v>1.635562</v>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Triple Point Resources Ltd. (“Triple Point”)</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>loss for December 31, 2022. As of December 31, 2023, the Company's ownership was diluted to 27.33% (December 31, 2022 - 28.83%), resulting in a dilution gain of</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O309" s="5" t="n">
+        <v>0.365182</v>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Point.</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>December 31 December</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O310" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Point.</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Point. total</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O311" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Point.</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Balance beginning of year 1,635,562</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Point.</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Initial investment -</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O313" s="5" t="n">
+        <v>1.288108</v>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Point.</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Share of net loss and comprehensive income (587,631)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O314" s="5" t="n">
+        <v>-0.062166</v>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Point.</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Dilution gain 365,182</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O315" s="5" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Point.</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Investment in Triple Point 1,413,113</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O316" s="5" t="n">
+        <v>1.635562</v>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Gain on investment in associate (Note 5)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N317" s="5" t="n">
+        <v>0.739049</v>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Dilution gain (Note 5)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N318" s="5" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation assets (Note 6)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N319" s="5" t="n">
+        <v>0.248911</v>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M320" s="5" t="n">
+        <v>0.020517</v>
+      </c>
+      <c r="N320" s="5" t="n">
+        <v>0.151873</v>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M321" s="5" t="n">
+        <v>0.053924</v>
+      </c>
+      <c r="N321" s="5" t="n">
+        <v>0.07940999999999999</v>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 10)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M322" s="5" t="n">
+        <v>-0.986461</v>
+      </c>
+      <c r="N322" s="5" t="n">
+        <v>-1.80447</v>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Marketing and communications</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M323" s="5" t="n">
+        <v>-0.651855</v>
+      </c>
+      <c r="N323" s="5" t="n">
+        <v>-0.793412</v>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Transfer agent, regulatory and professional fees</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M324" s="5" t="n">
+        <v>-0.093818</v>
+      </c>
+      <c r="N324" s="5" t="n">
+        <v>-0.433881</v>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Management and subcontract fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M325" s="5" t="n">
+        <v>-0.196916</v>
+      </c>
+      <c r="N325" s="5" t="n">
+        <v>-0.370687</v>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Office and other (Note11)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M326" s="5" t="n">
+        <v>-0.207544</v>
+      </c>
+      <c r="N326" s="5" t="n">
+        <v>-0.234003</v>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M327" s="5" t="n">
+        <v>0.083413</v>
+      </c>
+      <c r="N327" s="5" t="n">
+        <v>0.211102</v>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Conferences and travel</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M328" s="5" t="n">
+        <v>-2.2e-05</v>
+      </c>
+      <c r="N328" s="5" t="n">
+        <v>-0.118809</v>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Loss from equity accounted investment (Note 5)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N329" s="5" t="n">
+        <v>-0.062166</v>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Directors' fees</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M330" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N330" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M331" s="5" t="n">
+        <v>-0.001402</v>
+      </c>
+      <c r="N331" s="5" t="n">
+        <v>-0.003393</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M332" s="5" t="n">
+        <v>-2.17199</v>
+      </c>
+      <c r="N332" s="5" t="n">
+        <v>-2.45306</v>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Gain on disposal of mineral exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Net loss per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M333" s="5" t="n">
+        <v>-3.1e-08</v>
+      </c>
+      <c r="N333" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Weighted-average number of common shares outstanding -</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Weighted-average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F334" s="5" t="n">
+        <v>13.227399</v>
+      </c>
+      <c r="G334" s="5" t="n">
+        <v>36.883566</v>
+      </c>
+      <c r="H334" s="5" t="n">
+        <v>40.916671</v>
+      </c>
+      <c r="I334" s="5" t="n">
+        <v>43.420837</v>
+      </c>
+      <c r="J334" s="5" t="n">
+        <v>48.050004</v>
+      </c>
+      <c r="K334" s="5" t="n">
+        <v>48.050004</v>
+      </c>
+      <c r="L334" s="5" t="n">
+        <v>50.600004</v>
+      </c>
+      <c r="M334" s="5" t="n">
+        <v>69.573459</v>
+      </c>
+      <c r="N334" s="5" t="n">
+        <v>82.82726</v>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Management and subcontract fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" s="5" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="L335" s="5" t="n">
+        <v>-0.022487</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Transfer agent, regulatory and professional fees</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H336" s="5" t="n">
+        <v>-0.043224</v>
+      </c>
+      <c r="I336" s="5" t="n">
+        <v>-0.05615</v>
+      </c>
+      <c r="J336" s="5" t="n">
+        <v>-0.039993</v>
+      </c>
+      <c r="K336" s="5" t="n">
+        <v>-0.041505</v>
+      </c>
+      <c r="L336" s="5" t="n">
+        <v>-0.041446</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Office and other</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H337" s="5" t="n">
+        <v>-0.03631</v>
+      </c>
+      <c r="I337" s="5" t="n">
+        <v>-0.033782</v>
+      </c>
+      <c r="J337" s="5" t="n">
+        <v>-0.027721</v>
+      </c>
+      <c r="K337" s="5" t="n">
+        <v>-0.023832</v>
+      </c>
+      <c r="L337" s="5" t="n">
+        <v>-0.043516</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Conferences and travel</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H338" s="5" t="n">
+        <v>-0.000223</v>
+      </c>
+      <c r="I338" s="5" t="n">
+        <v>-0.003115</v>
+      </c>
+      <c r="J338" s="5" t="n">
+        <v>-0.001138</v>
+      </c>
+      <c r="K338" s="5" t="n">
+        <v>-0.008562999999999999</v>
+      </c>
+      <c r="L338" s="5" t="n">
+        <v>-0.026313</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K339" s="5" t="n">
+        <v>-0.000525</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>-0.000525</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expense</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J340" s="5" t="n">
+        <v>-0.003918</v>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L340" s="5" t="n">
+        <v>-0.00144</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 9 (b))</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H341" s="5" t="n">
+        <v>-0.013105</v>
+      </c>
+      <c r="I341" s="5" t="n">
+        <v>-0.002144</v>
+      </c>
+      <c r="J341" s="5" t="n">
+        <v>-0.02466</v>
+      </c>
+      <c r="K341" s="5" t="n">
+        <v>-0.111268</v>
+      </c>
+      <c r="L341" s="5" t="n">
+        <v>-0.078171</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H342" s="5" t="n">
+        <v>-0.191213</v>
+      </c>
+      <c r="I342" s="5" t="n">
+        <v>-0.170113</v>
+      </c>
+      <c r="J342" s="5" t="n">
+        <v>-0.141131</v>
+      </c>
+      <c r="K342" s="5" t="n">
+        <v>-0.196193</v>
+      </c>
+      <c r="L342" s="5" t="n">
+        <v>-0.213898</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Net loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H343" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="I343" s="5" t="n">
+        <v>-4e-09</v>
+      </c>
+      <c r="J343" s="5" t="n">
+        <v>-3e-09</v>
+      </c>
+      <c r="K343" s="5" t="n">
+        <v>-4e-09</v>
+      </c>
+      <c r="L343" s="5" t="n">
+        <v>-4e-09</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H344" s="5" t="n">
+        <v>0.002493</v>
+      </c>
+      <c r="I344" s="5" t="n">
+        <v>0.000358</v>
+      </c>
+      <c r="J344" s="5" t="n">
+        <v>0.000348</v>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Other income (Note 8 (c ))</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J345" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Management and subcontract fees</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H346" s="5" t="n">
+        <v>-0.08834400000000001</v>
+      </c>
+      <c r="I346" s="5" t="n">
+        <v>-0.06278</v>
+      </c>
+      <c r="J346" s="5" t="n">
+        <v>-0.034049</v>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Directors' fees</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H347" s="5" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="I347" s="5" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="J347" s="5" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Management and subcontract fees</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F348" s="5" t="n">
+        <v>0.071543</v>
+      </c>
+      <c r="G348" s="5" t="n">
+        <v>0.120437</v>
+      </c>
+      <c r="H348" s="5" t="n">
+        <v>0.08834400000000001</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Transfer agent, regulatory and professional fees</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F349" s="5" t="n">
+        <v>0.027569</v>
+      </c>
+      <c r="G349" s="5" t="n">
+        <v>0.045395</v>
+      </c>
+      <c r="H349" s="5" t="n">
+        <v>0.043224</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Office and other</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F350" s="5" t="n">
+        <v>0.005466</v>
+      </c>
+      <c r="G350" s="5" t="n">
+        <v>0.036278</v>
+      </c>
+      <c r="H350" s="5" t="n">
+        <v>0.03631</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 9 b))</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G351" s="5" t="n">
+        <v>0.02711</v>
+      </c>
+      <c r="H351" s="5" t="n">
+        <v>0.013105</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Conferences and travel</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F352" s="5" t="n">
+        <v>0.011787</v>
+      </c>
+      <c r="G352" s="5" t="n">
+        <v>0.017952</v>
+      </c>
+      <c r="H352" s="5" t="n">
+        <v>0.000223</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Directors' fees</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G353" s="5" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="H353" s="5" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Website development</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G354" s="5" t="n">
+        <v>0.006428</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>General and administrative expenses total</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F355" s="5" t="n">
+        <v>0.116365</v>
+      </c>
+      <c r="G355" s="5" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="H355" s="5" t="n">
+        <v>0.193706</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F356" s="5" t="n">
+        <v>0.002914</v>
+      </c>
+      <c r="G356" s="5" t="n">
+        <v>0.004173</v>
+      </c>
+      <c r="H356" s="5" t="n">
+        <v>0.002493</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F357" s="5" t="n">
+        <v>-0.113451</v>
+      </c>
+      <c r="G357" s="5" t="n">
+        <v>-0.261927</v>
+      </c>
+      <c r="H357" s="5" t="n">
+        <v>-0.191213</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Net loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F358" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G358" s="5" t="n">
+        <v>-7e-09</v>
+      </c>
+      <c r="H358" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
           <t>Expenses (Other Income)</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>General and administrative (Note 10 &amp; 11) $</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F359" s="5" t="n">
+        <v>0.116365</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Expenses (Other Income)</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F360" s="5" t="n">
+        <v>-0.002914</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Expenses (Other Income)</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Net loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F361" s="5" t="n">
+        <v>-0.113451</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Expenses (Other Income)</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F362" s="5" t="n">
+        <v>-0.113451</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Expenses (Other Income)</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
         <is>
           <t>Net loss per share - basic and diluted $</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
+      <c r="D363" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F302" s="5" t="n">
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F363" s="5" t="n">
         <v>-1e-08</v>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q302" t="inlineStr">
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
         <is>
           <t>-</t>
         </is>
